--- a/RP7.4_weights.xlsx
+++ b/RP7.4_weights.xlsx
@@ -1218,7 +1218,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Pesi/soglie provvisori, da confermare in workshop produzione/qualita/manutenzione (come OR6.8 / paper O-TSA).</t>
+          <t>Pesi/soglie provvisori, da confermare in workshop produzione/qualita/manutenzione.</t>
         </is>
       </c>
     </row>
